--- a/assets/tame_template.xlsx
+++ b/assets/tame_template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Raivis.Biskaps\Documents\Claude\Projects\Horizon pārdošana\docs-qa\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Raivis.Biskaps\Documents\Claude\Projects\Horizon pārdošana\docs-qa\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8205470-F6FD-492C-B9F1-723003A9660D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D6B3CD4-9830-404E-80B4-1C8361CBB008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -407,7 +407,7 @@
       <name val="&quot;Source Sans Pro&quot;, Arial"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -422,18 +422,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -584,19 +578,6 @@
         <color rgb="FFE0E8EC"/>
       </left>
       <right/>
-      <top style="thin">
-        <color rgb="FFE0E8EC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFE0E8EC"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color rgb="FFE0E8EC"/>
-      </left>
-      <right/>
       <top/>
       <bottom/>
       <diagonal/>
@@ -647,7 +628,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -672,7 +653,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -694,25 +675,16 @@
     <xf numFmtId="164" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -734,33 +706,30 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1137,10 +1106,10 @@
       <c r="H1" s="7"/>
     </row>
     <row r="2" spans="1:8" ht="33" customHeight="1">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="43"/>
+      <c r="B2" s="39"/>
       <c r="C2" s="8" t="s">
         <v>44</v>
       </c>
@@ -1181,7 +1150,7 @@
       <c r="D4" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="19">
+      <c r="E4" s="18">
         <v>3</v>
       </c>
       <c r="F4" s="11">
@@ -1203,7 +1172,7 @@
       <c r="D5" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="19">
+      <c r="E5" s="18">
         <v>8</v>
       </c>
       <c r="F5" s="11">
@@ -1212,27 +1181,27 @@
       <c r="G5" s="13">
         <v>640</v>
       </c>
-      <c r="H5" s="20"/>
+      <c r="H5" s="19"/>
     </row>
     <row r="6" spans="1:8" ht="45">
       <c r="A6" s="14" t="s">
         <v>49</v>
       </c>
       <c r="B6" s="14"/>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="8" t="s">
         <v>10</v>
       </c>
       <c r="D6" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="19"/>
+      <c r="E6" s="18"/>
       <c r="F6" s="11">
         <v>80</v>
       </c>
       <c r="G6" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="H6" s="20"/>
+      <c r="H6" s="19"/>
     </row>
     <row r="7" spans="1:8" ht="75">
       <c r="A7" s="14" t="s">
@@ -1245,7 +1214,7 @@
       <c r="D7" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="19">
+      <c r="E7" s="18">
         <v>8</v>
       </c>
       <c r="F7" s="11">
@@ -1256,127 +1225,127 @@
       </c>
       <c r="H7" s="7"/>
     </row>
-    <row r="8" spans="1:8" ht="62.4">
+    <row r="8" spans="1:8" ht="60">
       <c r="A8" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="24" t="s">
+      <c r="C8" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="25" t="s">
+      <c r="D8" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="E8" s="26"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="28">
+      <c r="E8" s="23"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="25">
         <v>960</v>
       </c>
-      <c r="H8" s="20"/>
+      <c r="H8" s="19"/>
     </row>
     <row r="9" spans="1:8" ht="15.6">
       <c r="A9" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="24" t="s">
+      <c r="C9" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="29">
+      <c r="D9" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="26">
         <v>2</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="27">
         <v>80</v>
       </c>
-      <c r="G9" s="28">
+      <c r="G9" s="25">
         <v>160</v>
       </c>
-      <c r="H9" s="20"/>
-    </row>
-    <row r="10" spans="1:8" ht="31.2">
+      <c r="H9" s="19"/>
+    </row>
+    <row r="10" spans="1:8" ht="30">
       <c r="A10" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="24" t="s">
+      <c r="C10" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="29">
+      <c r="D10" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="26">
         <v>10</v>
       </c>
-      <c r="F10" s="30">
+      <c r="F10" s="27">
         <v>80</v>
       </c>
-      <c r="G10" s="28">
+      <c r="G10" s="25">
         <v>800</v>
       </c>
-      <c r="H10" s="20"/>
-    </row>
-    <row r="11" spans="1:8" ht="46.8">
+      <c r="H10" s="19"/>
+    </row>
+    <row r="11" spans="1:8" ht="60">
       <c r="A11" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="24" t="s">
+      <c r="C11" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D11" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" s="29">
+      <c r="D11" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="26">
         <v>5</v>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="27">
         <v>80</v>
       </c>
-      <c r="G11" s="28">
+      <c r="G11" s="25">
         <v>400</v>
       </c>
-      <c r="H11" s="20"/>
-    </row>
-    <row r="12" spans="1:8" ht="46.8">
+      <c r="H11" s="19"/>
+    </row>
+    <row r="12" spans="1:8" ht="45">
       <c r="A12" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="B12" s="22" t="s">
+      <c r="B12" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="24" t="s">
+      <c r="C12" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D12" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" s="29">
+      <c r="D12" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="26">
         <v>5</v>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="27">
         <v>80</v>
       </c>
-      <c r="G12" s="28">
+      <c r="G12" s="25">
         <v>400</v>
       </c>
-      <c r="H12" s="20"/>
+      <c r="H12" s="19"/>
     </row>
     <row r="13" spans="1:8" ht="345">
-      <c r="A13" s="44" t="s">
+      <c r="A13" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="B13" s="31" t="s">
+      <c r="B13" s="28" t="s">
         <v>18</v>
       </c>
       <c r="C13" s="8" t="s">
@@ -1393,10 +1362,10 @@
       <c r="H13" s="7"/>
     </row>
     <row r="14" spans="1:8" ht="31.2">
-      <c r="A14" s="44" t="s">
+      <c r="A14" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="B14" s="31" t="s">
+      <c r="B14" s="28" t="s">
         <v>18</v>
       </c>
       <c r="C14" s="8" t="s">
@@ -1405,7 +1374,7 @@
       <c r="D14" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="19"/>
+      <c r="E14" s="18"/>
       <c r="F14" s="11">
         <v>80</v>
       </c>
@@ -1415,10 +1384,10 @@
       <c r="H14" s="7"/>
     </row>
     <row r="15" spans="1:8" ht="180">
-      <c r="A15" s="44" t="s">
+      <c r="A15" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="B15" s="22" t="s">
+      <c r="B15" s="20" t="s">
         <v>21</v>
       </c>
       <c r="C15" s="8" t="s">
@@ -1435,10 +1404,10 @@
       <c r="H15" s="7"/>
     </row>
     <row r="16" spans="1:8" ht="31.2">
-      <c r="A16" s="44" t="s">
+      <c r="A16" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="B16" s="22" t="s">
+      <c r="B16" s="20" t="s">
         <v>21</v>
       </c>
       <c r="C16" s="8" t="s">
@@ -1447,7 +1416,7 @@
       <c r="D16" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="E16" s="19">
+      <c r="E16" s="18">
         <v>3</v>
       </c>
       <c r="F16" s="11">
@@ -1459,10 +1428,10 @@
       <c r="H16" s="7"/>
     </row>
     <row r="17" spans="1:8" ht="210">
-      <c r="A17" s="44" t="s">
+      <c r="A17" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="B17" s="31" t="s">
+      <c r="B17" s="28" t="s">
         <v>24</v>
       </c>
       <c r="C17" s="8" t="s">
@@ -1479,10 +1448,10 @@
       <c r="H17" s="7"/>
     </row>
     <row r="18" spans="1:8" ht="31.2">
-      <c r="A18" s="44" t="s">
+      <c r="A18" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="B18" s="31" t="s">
+      <c r="B18" s="28" t="s">
         <v>24</v>
       </c>
       <c r="C18" s="8" t="s">
@@ -1491,7 +1460,7 @@
       <c r="D18" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="E18" s="19"/>
+      <c r="E18" s="18"/>
       <c r="F18" s="11">
         <v>80</v>
       </c>
@@ -1500,14 +1469,14 @@
       </c>
       <c r="H18" s="7"/>
     </row>
-    <row r="19" spans="1:8" ht="78">
-      <c r="A19" s="44" t="s">
+    <row r="19" spans="1:8" ht="75">
+      <c r="A19" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="B19" s="31" t="s">
+      <c r="B19" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="C19" s="32" t="s">
+      <c r="C19" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D19" s="15" t="s">
@@ -1521,10 +1490,10 @@
       <c r="H19" s="7"/>
     </row>
     <row r="20" spans="1:8" ht="31.2">
-      <c r="A20" s="44" t="s">
+      <c r="A20" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="B20" s="31" t="s">
+      <c r="B20" s="28" t="s">
         <v>27</v>
       </c>
       <c r="C20" s="8" t="s">
@@ -1533,7 +1502,7 @@
       <c r="D20" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="E20" s="19"/>
+      <c r="E20" s="18"/>
       <c r="F20" s="11">
         <v>80</v>
       </c>
@@ -1543,10 +1512,10 @@
       <c r="H20" s="7"/>
     </row>
     <row r="21" spans="1:8" ht="315">
-      <c r="A21" s="44" t="s">
+      <c r="A21" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="B21" s="31" t="s">
+      <c r="B21" s="28" t="s">
         <v>29</v>
       </c>
       <c r="C21" s="8" t="s">
@@ -1563,10 +1532,10 @@
       <c r="H21" s="7"/>
     </row>
     <row r="22" spans="1:8" ht="31.2">
-      <c r="A22" s="44" t="s">
+      <c r="A22" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="B22" s="31" t="s">
+      <c r="B22" s="28" t="s">
         <v>29</v>
       </c>
       <c r="C22" s="8" t="s">
@@ -1575,7 +1544,7 @@
       <c r="D22" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="E22" s="19" t="s">
+      <c r="E22" s="18" t="s">
         <v>46</v>
       </c>
       <c r="F22" s="11">
@@ -1585,10 +1554,10 @@
       <c r="H22" s="7"/>
     </row>
     <row r="23" spans="1:8" ht="120">
-      <c r="A23" s="44" t="s">
+      <c r="A23" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="B23" s="31" t="s">
+      <c r="B23" s="28" t="s">
         <v>31</v>
       </c>
       <c r="C23" s="8" t="s">
@@ -1605,10 +1574,10 @@
       <c r="H23" s="7"/>
     </row>
     <row r="24" spans="1:8" ht="15.6">
-      <c r="A24" s="44" t="s">
+      <c r="A24" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="B24" s="31" t="s">
+      <c r="B24" s="28" t="s">
         <v>31</v>
       </c>
       <c r="C24" s="8" t="s">
@@ -1617,7 +1586,7 @@
       <c r="D24" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="E24" s="19" t="s">
+      <c r="E24" s="18" t="s">
         <v>46</v>
       </c>
       <c r="F24" s="11">
@@ -1627,10 +1596,10 @@
       <c r="H24" s="7"/>
     </row>
     <row r="25" spans="1:8" ht="150">
-      <c r="A25" s="44" t="s">
+      <c r="A25" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="B25" s="31" t="s">
+      <c r="B25" s="28" t="s">
         <v>34</v>
       </c>
       <c r="C25" s="8" t="s">
@@ -1647,10 +1616,10 @@
       <c r="H25" s="7"/>
     </row>
     <row r="26" spans="1:8" ht="30">
-      <c r="A26" s="44" t="s">
+      <c r="A26" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="B26" s="31" t="s">
+      <c r="B26" s="28" t="s">
         <v>34</v>
       </c>
       <c r="C26" s="8" t="s">
@@ -1659,7 +1628,7 @@
       <c r="D26" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="E26" s="19">
+      <c r="E26" s="18">
         <v>4</v>
       </c>
       <c r="F26" s="11">
@@ -1671,10 +1640,10 @@
       <c r="H26" s="7"/>
     </row>
     <row r="27" spans="1:8" ht="75">
-      <c r="A27" s="44" t="s">
+      <c r="A27" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="B27" s="31" t="s">
+      <c r="B27" s="28" t="s">
         <v>37</v>
       </c>
       <c r="C27" s="8" t="s">
@@ -1689,10 +1658,10 @@
       <c r="H27" s="7"/>
     </row>
     <row r="28" spans="1:8" ht="120">
-      <c r="A28" s="44" t="s">
+      <c r="A28" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="B28" s="31" t="s">
+      <c r="B28" s="28" t="s">
         <v>37</v>
       </c>
       <c r="C28" s="8" t="s">
@@ -1709,10 +1678,10 @@
       <c r="H28" s="7"/>
     </row>
     <row r="29" spans="1:8" ht="31.2">
-      <c r="A29" s="44" t="s">
+      <c r="A29" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="B29" s="31" t="s">
+      <c r="B29" s="28" t="s">
         <v>37</v>
       </c>
       <c r="C29" s="8" t="s">
@@ -1729,10 +1698,10 @@
       <c r="H29" s="7"/>
     </row>
     <row r="30" spans="1:8" ht="105">
-      <c r="A30" s="44" t="s">
+      <c r="A30" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="B30" s="31" t="s">
+      <c r="B30" s="28" t="s">
         <v>37</v>
       </c>
       <c r="C30" s="8" t="s">
@@ -1741,7 +1710,7 @@
       <c r="D30" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="E30" s="19"/>
+      <c r="E30" s="18"/>
       <c r="F30" s="11">
         <v>80</v>
       </c>
@@ -1751,31 +1720,31 @@
       <c r="H30" s="7"/>
     </row>
     <row r="31" spans="1:8" ht="39" customHeight="1" thickBot="1">
-      <c r="A31" s="42" t="s">
+      <c r="A31" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="B31" s="42"/>
-      <c r="C31" s="33" t="s">
+      <c r="B31" s="38"/>
+      <c r="C31" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="D31" s="34" t="s">
-        <v>8</v>
-      </c>
-      <c r="E31" s="35"/>
-      <c r="F31" s="36">
+      <c r="D31" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="31"/>
+      <c r="F31" s="32">
         <v>80</v>
       </c>
-      <c r="G31" s="37"/>
-      <c r="H31" s="23"/>
+      <c r="G31" s="33"/>
+      <c r="H31" s="21"/>
     </row>
     <row r="32" spans="1:8" ht="15.6">
-      <c r="A32" s="38"/>
-      <c r="B32" s="38"/>
-      <c r="C32" s="39"/>
-      <c r="D32" s="40"/>
-      <c r="E32" s="40"/>
-      <c r="F32" s="41"/>
-      <c r="G32" s="40"/>
+      <c r="A32" s="34"/>
+      <c r="B32" s="34"/>
+      <c r="C32" s="35"/>
+      <c r="D32" s="36"/>
+      <c r="E32" s="36"/>
+      <c r="F32" s="37"/>
+      <c r="G32" s="36"/>
       <c r="H32" s="1"/>
     </row>
   </sheetData>
